--- a/Daily_Report/Top 7 broker List with its Turnover 2024-09-26.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-09-26.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="273">
   <si>
     <t>Date: 2024-09-26</t>
   </si>
@@ -59,109 +59,109 @@
     <t>7</t>
   </si>
   <si>
+    <t>Naasa Securities Co. Ltd.</t>
+  </si>
+  <si>
+    <t>Vision Securities Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Imperial Securities Co .Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Sani Securities Company Limited</t>
+  </si>
+  <si>
+    <t>Online Securities Pvt.Ltd</t>
+  </si>
+  <si>
+    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
+  </si>
+  <si>
     <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
   </si>
   <si>
-    <t>Naasa Securities Co. Ltd.</t>
-  </si>
-  <si>
-    <t>Sani Securities Company Limited</t>
-  </si>
-  <si>
-    <t>Imperial Securities Co .Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Dynamic Money Managers Securities Pvt.Ltd</t>
-  </si>
-  <si>
-    <t>Vision Securities Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
+    <t>58</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>57</t>
   </si>
   <si>
     <t>38</t>
   </si>
   <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>996,533,796.0</t>
-  </si>
-  <si>
-    <t>485,370,275.22</t>
-  </si>
-  <si>
-    <t>446,942,435.29</t>
-  </si>
-  <si>
-    <t>415,435,769.8</t>
-  </si>
-  <si>
-    <t>341,099,702.1</t>
-  </si>
-  <si>
-    <t>292,225,074.89</t>
-  </si>
-  <si>
-    <t>279,690,337.6</t>
-  </si>
-  <si>
-    <t>103,375,794.3</t>
-  </si>
-  <si>
-    <t>340,511,005.92</t>
-  </si>
-  <si>
-    <t>111,530,581.6</t>
-  </si>
-  <si>
-    <t>207,512,173.4</t>
-  </si>
-  <si>
-    <t>253,304,130.4</t>
-  </si>
-  <si>
-    <t>157,984,458.5</t>
-  </si>
-  <si>
-    <t>172,107,140.2</t>
-  </si>
-  <si>
-    <t>893,158,001.7</t>
-  </si>
-  <si>
-    <t>144,859,269.3</t>
-  </si>
-  <si>
-    <t>335,411,853.7</t>
-  </si>
-  <si>
-    <t>207,923,596.4</t>
-  </si>
-  <si>
-    <t>87,795,571.7</t>
-  </si>
-  <si>
-    <t>134,240,616.4</t>
-  </si>
-  <si>
-    <t>107,583,197.4</t>
+    <t>445,283,669.78</t>
+  </si>
+  <si>
+    <t>381,685,034.22</t>
+  </si>
+  <si>
+    <t>343,193,770.14</t>
+  </si>
+  <si>
+    <t>323,776,648.66</t>
+  </si>
+  <si>
+    <t>304,280,102.6</t>
+  </si>
+  <si>
+    <t>290,293,291.19</t>
+  </si>
+  <si>
+    <t>253,885,160.0</t>
+  </si>
+  <si>
+    <t>246,873,974.9</t>
+  </si>
+  <si>
+    <t>188,342,553.42</t>
+  </si>
+  <si>
+    <t>159,058,663.19</t>
+  </si>
+  <si>
+    <t>136,994,971.5</t>
+  </si>
+  <si>
+    <t>164,127,763.0</t>
+  </si>
+  <si>
+    <t>146,521,922.69</t>
+  </si>
+  <si>
+    <t>125,628,159.3</t>
+  </si>
+  <si>
+    <t>198,409,694.88</t>
+  </si>
+  <si>
+    <t>193,342,480.8</t>
+  </si>
+  <si>
+    <t>184,135,106.95</t>
+  </si>
+  <si>
+    <t>186,781,677.17</t>
+  </si>
+  <si>
+    <t>140,152,339.6</t>
+  </si>
+  <si>
+    <t>143,771,368.5</t>
+  </si>
+  <si>
+    <t>128,257,000.7</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -179,343 +179,322 @@
     <t>% of turnover</t>
   </si>
   <si>
-    <t>KKHC</t>
-  </si>
-  <si>
-    <t>24,217,119.9</t>
-  </si>
-  <si>
-    <t>SADBL</t>
-  </si>
-  <si>
-    <t>18,651,150.0</t>
-  </si>
-  <si>
-    <t>FOWAD</t>
-  </si>
-  <si>
-    <t>7,059,107.1</t>
+    <t>API</t>
+  </si>
+  <si>
+    <t>15,504,899.4</t>
+  </si>
+  <si>
+    <t>HATHY</t>
+  </si>
+  <si>
+    <t>12,005,219.0</t>
+  </si>
+  <si>
+    <t>VLUCL</t>
+  </si>
+  <si>
+    <t>9,137,393.0</t>
+  </si>
+  <si>
+    <t>KBL</t>
+  </si>
+  <si>
+    <t>7,454,050.8</t>
   </si>
   <si>
     <t>UPPER</t>
   </si>
   <si>
-    <t>7,013,188.0</t>
+    <t>7,365,439.1</t>
+  </si>
+  <si>
+    <t>23,483,453.5</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>9,283,866.19</t>
+  </si>
+  <si>
+    <t>SHIVM</t>
+  </si>
+  <si>
+    <t>6,457,411.0</t>
+  </si>
+  <si>
+    <t>LICN</t>
+  </si>
+  <si>
+    <t>6,112,989.0</t>
+  </si>
+  <si>
+    <t>SRLI</t>
+  </si>
+  <si>
+    <t>5,268,128.0</t>
+  </si>
+  <si>
+    <t>19,082,798.89</t>
+  </si>
+  <si>
+    <t>SMJC</t>
+  </si>
+  <si>
+    <t>8,315,524.2</t>
+  </si>
+  <si>
+    <t>CIT</t>
+  </si>
+  <si>
+    <t>5,395,642.4</t>
+  </si>
+  <si>
+    <t>HHL</t>
+  </si>
+  <si>
+    <t>4,070,314.0</t>
+  </si>
+  <si>
+    <t>3,915,481.8</t>
+  </si>
+  <si>
+    <t>10,056,884.1</t>
+  </si>
+  <si>
+    <t>NIMB</t>
+  </si>
+  <si>
+    <t>6,341,894.8</t>
+  </si>
+  <si>
+    <t>GFCL</t>
+  </si>
+  <si>
+    <t>6,169,538.5</t>
+  </si>
+  <si>
+    <t>PROFL</t>
+  </si>
+  <si>
+    <t>4,845,288.4</t>
+  </si>
+  <si>
+    <t>4,651,553.09</t>
+  </si>
+  <si>
+    <t>26,111,509.1</t>
+  </si>
+  <si>
+    <t>NIL</t>
+  </si>
+  <si>
+    <t>6,299,900.0</t>
+  </si>
+  <si>
+    <t>5,804,728.6</t>
+  </si>
+  <si>
+    <t>5,144,390.5</t>
+  </si>
+  <si>
+    <t>4,763,321.4</t>
+  </si>
+  <si>
+    <t>17,008,396.5</t>
+  </si>
+  <si>
+    <t>12,201,930.9</t>
+  </si>
+  <si>
+    <t>3,809,508.0</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>3,437,883.0</t>
+  </si>
+  <si>
+    <t>AHPC</t>
+  </si>
+  <si>
+    <t>3,257,144.1</t>
+  </si>
+  <si>
+    <t>21,586,276.1</t>
+  </si>
+  <si>
+    <t>5,733,865.2</t>
+  </si>
+  <si>
+    <t>4,438,810.4</t>
+  </si>
+  <si>
+    <t>CFCL</t>
+  </si>
+  <si>
+    <t>3,747,336.0</t>
+  </si>
+  <si>
+    <t>HDHPC</t>
+  </si>
+  <si>
+    <t>3,239,751.0</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>24,372,392.8</t>
+  </si>
+  <si>
+    <t>USHL</t>
+  </si>
+  <si>
+    <t>13,994,538.2</t>
+  </si>
+  <si>
+    <t>DORDI</t>
+  </si>
+  <si>
+    <t>8,540,986.5</t>
+  </si>
+  <si>
+    <t>SLBBL</t>
+  </si>
+  <si>
+    <t>8,406,578.0</t>
+  </si>
+  <si>
+    <t>HIDCLP</t>
+  </si>
+  <si>
+    <t>6,347,796.1</t>
+  </si>
+  <si>
+    <t>16,005,733.4</t>
+  </si>
+  <si>
+    <t>10,322,093.69</t>
+  </si>
+  <si>
+    <t>RFPL</t>
+  </si>
+  <si>
+    <t>7,493,951.5</t>
+  </si>
+  <si>
+    <t>MKCL</t>
+  </si>
+  <si>
+    <t>7,352,591.0</t>
+  </si>
+  <si>
+    <t>5,599,981.3</t>
+  </si>
+  <si>
+    <t>16,276,375.2</t>
+  </si>
+  <si>
+    <t>NLG</t>
+  </si>
+  <si>
+    <t>10,078,582.69</t>
   </si>
   <si>
     <t>MPFL</t>
   </si>
   <si>
-    <t>6,751,163.0</t>
-  </si>
-  <si>
-    <t>KBL</t>
-  </si>
-  <si>
-    <t>194,444,559.5</t>
-  </si>
-  <si>
-    <t>NRIC</t>
-  </si>
-  <si>
-    <t>28,866,268.0</t>
-  </si>
-  <si>
-    <t>MMKJL</t>
-  </si>
-  <si>
-    <t>24,905,250.0</t>
-  </si>
-  <si>
-    <t>10,201,726.0</t>
-  </si>
-  <si>
-    <t>USHL</t>
-  </si>
-  <si>
-    <t>8,318,064.5</t>
-  </si>
-  <si>
-    <t>ILI</t>
-  </si>
-  <si>
-    <t>23,062,369.0</t>
-  </si>
-  <si>
-    <t>9,579,460.0</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>9,536,046.1</t>
-  </si>
-  <si>
-    <t>5,425,660.0</t>
-  </si>
-  <si>
-    <t>SWBBL</t>
-  </si>
-  <si>
-    <t>5,416,058.0</t>
-  </si>
-  <si>
-    <t>58,440,264.5</t>
-  </si>
-  <si>
-    <t>SMJC</t>
-  </si>
-  <si>
-    <t>48,651,044.0</t>
-  </si>
-  <si>
-    <t>GVL</t>
-  </si>
-  <si>
-    <t>25,620,750.0</t>
-  </si>
-  <si>
-    <t>EDBL</t>
-  </si>
-  <si>
-    <t>11,859,172.0</t>
-  </si>
-  <si>
-    <t>HDHPC</t>
-  </si>
-  <si>
-    <t>9,716,981.3</t>
-  </si>
-  <si>
-    <t>NTC</t>
-  </si>
-  <si>
-    <t>78,267,527.0</t>
-  </si>
-  <si>
-    <t>PMLI</t>
-  </si>
-  <si>
-    <t>73,919,285.4</t>
-  </si>
-  <si>
-    <t>MSLB</t>
-  </si>
-  <si>
-    <t>20,044,483.6</t>
-  </si>
-  <si>
-    <t>ADBL</t>
-  </si>
-  <si>
-    <t>17,524,244.3</t>
-  </si>
-  <si>
-    <t>9,909,745.0</t>
-  </si>
-  <si>
-    <t>UPCL</t>
-  </si>
-  <si>
-    <t>24,715,637.0</t>
-  </si>
-  <si>
-    <t>SHINE</t>
-  </si>
-  <si>
-    <t>21,345,534.0</t>
-  </si>
-  <si>
-    <t>HLI</t>
-  </si>
-  <si>
-    <t>20,936,879.0</t>
-  </si>
-  <si>
-    <t>12,308,786.0</t>
-  </si>
-  <si>
-    <t>8,373,038.7</t>
-  </si>
-  <si>
-    <t>AHPC</t>
-  </si>
-  <si>
-    <t>48,907,880.0</t>
+    <t>7,070,716.4</t>
+  </si>
+  <si>
+    <t>6,502,188.3</t>
+  </si>
+  <si>
+    <t>5,956,775.6</t>
+  </si>
+  <si>
+    <t>SARBTM</t>
+  </si>
+  <si>
+    <t>22,451,873.3</t>
+  </si>
+  <si>
+    <t>18,337,910.6</t>
   </si>
   <si>
     <t>RURU</t>
   </si>
   <si>
-    <t>31,776,900.0</t>
-  </si>
-  <si>
-    <t>SRLI</t>
-  </si>
-  <si>
-    <t>28,481,742.5</t>
-  </si>
-  <si>
-    <t>CZBIL</t>
-  </si>
-  <si>
-    <t>10,794,850.0</t>
-  </si>
-  <si>
-    <t>3,908,714.3</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>751,359,500.3</t>
-  </si>
-  <si>
-    <t>46,766,000.0</t>
-  </si>
-  <si>
-    <t>23,499,785.2</t>
-  </si>
-  <si>
-    <t>SONA</t>
-  </si>
-  <si>
-    <t>20,368,504.5</t>
-  </si>
-  <si>
-    <t>5,075,598.4</t>
+    <t>10,056,784.0</t>
+  </si>
+  <si>
+    <t>9,192,778.19</t>
   </si>
   <si>
     <t>CGH</t>
   </si>
   <si>
-    <t>25,347,057.0</t>
-  </si>
-  <si>
-    <t>MFIL</t>
-  </si>
-  <si>
-    <t>15,616,898.0</t>
+    <t>8,734,478.5</t>
   </si>
   <si>
     <t>NRN</t>
   </si>
   <si>
-    <t>12,911,181.0</t>
-  </si>
-  <si>
-    <t>8,626,667.0</t>
-  </si>
-  <si>
-    <t>RAWA</t>
-  </si>
-  <si>
-    <t>7,421,377.4</t>
-  </si>
-  <si>
-    <t>84,471,288.0</t>
-  </si>
-  <si>
-    <t>31,619,731.2</t>
-  </si>
-  <si>
-    <t>29,295,000.0</t>
-  </si>
-  <si>
-    <t>UMHL</t>
-  </si>
-  <si>
-    <t>26,970,000.0</t>
-  </si>
-  <si>
-    <t>17,993,121.0</t>
-  </si>
-  <si>
-    <t>MKJC</t>
-  </si>
-  <si>
-    <t>39,990,000.0</t>
-  </si>
-  <si>
-    <t>EBL</t>
-  </si>
-  <si>
-    <t>28,643,880.0</t>
-  </si>
-  <si>
-    <t>HIDCL</t>
-  </si>
-  <si>
-    <t>14,979,716.3</t>
-  </si>
-  <si>
-    <t>14,167,874.3</t>
-  </si>
-  <si>
-    <t>13,005,751.0</t>
-  </si>
-  <si>
-    <t>28,257,487.3</t>
-  </si>
-  <si>
-    <t>NLG</t>
-  </si>
-  <si>
-    <t>11,993,852.0</t>
-  </si>
-  <si>
-    <t>7,295,896.7</t>
-  </si>
-  <si>
-    <t>4,314,450.0</t>
-  </si>
-  <si>
-    <t>SARBTM</t>
-  </si>
-  <si>
-    <t>3,427,527.5</t>
-  </si>
-  <si>
-    <t>28,244,261.3</t>
-  </si>
-  <si>
-    <t>26,166,949.0</t>
-  </si>
-  <si>
-    <t>NFS</t>
-  </si>
-  <si>
-    <t>9,806,953.69</t>
-  </si>
-  <si>
-    <t>MEN</t>
-  </si>
-  <si>
-    <t>8,687,749.0</t>
-  </si>
-  <si>
-    <t>GFCL</t>
-  </si>
-  <si>
-    <t>4,660,475.09</t>
-  </si>
-  <si>
-    <t>22,170,793.0</t>
-  </si>
-  <si>
-    <t>12,422,219.0</t>
-  </si>
-  <si>
-    <t>GUFL</t>
-  </si>
-  <si>
-    <t>6,233,775.0</t>
-  </si>
-  <si>
-    <t>5,809,548.0</t>
-  </si>
-  <si>
-    <t>5,156,202.59</t>
+    <t>15,934,830.4</t>
+  </si>
+  <si>
+    <t>12,846,124.2</t>
+  </si>
+  <si>
+    <t>11,570,836.8</t>
+  </si>
+  <si>
+    <t>UNLB</t>
+  </si>
+  <si>
+    <t>5,063,457.2</t>
+  </si>
+  <si>
+    <t>4,708,483.0</t>
+  </si>
+  <si>
+    <t>19,700,968.89</t>
+  </si>
+  <si>
+    <t>7,932,322.4</t>
+  </si>
+  <si>
+    <t>5,672,274.0</t>
+  </si>
+  <si>
+    <t>CLI</t>
+  </si>
+  <si>
+    <t>4,248,916.4</t>
+  </si>
+  <si>
+    <t>3,935,483.0</t>
+  </si>
+  <si>
+    <t>15,075,522.0</t>
+  </si>
+  <si>
+    <t>10,847,127.5</t>
+  </si>
+  <si>
+    <t>9,743,774.9</t>
+  </si>
+  <si>
+    <t>CHDC</t>
+  </si>
+  <si>
+    <t>5,956,991.5</t>
+  </si>
+  <si>
+    <t>5,115,727.5</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -533,112 +512,109 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>770,881,019.3</t>
-  </si>
-  <si>
-    <t>178,119,571.2</t>
-  </si>
-  <si>
-    <t>167,103,410.8</t>
-  </si>
-  <si>
-    <t>HHL</t>
-  </si>
-  <si>
-    <t>128,666,804.5</t>
-  </si>
-  <si>
-    <t>126,334,187.8</t>
+    <t>479,967,224.5</t>
+  </si>
+  <si>
+    <t>177,350,357.7</t>
+  </si>
+  <si>
+    <t>142,552,855.19</t>
+  </si>
+  <si>
+    <t>138,544,541.4</t>
+  </si>
+  <si>
+    <t>133,936,613.0</t>
+  </si>
+  <si>
+    <t>Hydro Power</t>
+  </si>
+  <si>
+    <t>1,513,514,644.0</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>1,768,267,573.5</t>
-  </si>
-  <si>
-    <t>Hydro Power</t>
-  </si>
-  <si>
-    <t>1,293,621,171.8</t>
+    <t>1,156,179,064.48</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>491,347,954.7</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>315,047,688.39</t>
+  </si>
+  <si>
+    <t>Non Life Insurance</t>
+  </si>
+  <si>
+    <t>281,368,651.1</t>
+  </si>
+  <si>
+    <t>Commercial Banks</t>
+  </si>
+  <si>
+    <t>273,308,626.7</t>
+  </si>
+  <si>
+    <t>Microfinance</t>
+  </si>
+  <si>
+    <t>246,860,889.8</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>267,931,073.2</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>238,380,333.6</t>
-  </si>
-  <si>
-    <t>Microfinance</t>
-  </si>
-  <si>
-    <t>228,218,357.7</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>219,950,545.4</t>
-  </si>
-  <si>
-    <t>Commercial Banks</t>
-  </si>
-  <si>
-    <t>210,486,422.2</t>
-  </si>
-  <si>
-    <t>Non Life Insurance</t>
-  </si>
-  <si>
-    <t>153,193,734.0</t>
+    <t>238,771,827.9</t>
+  </si>
+  <si>
+    <t>Manufacturing And Processing</t>
+  </si>
+  <si>
+    <t>100,709,623.0</t>
+  </si>
+  <si>
+    <t>Life Insurance</t>
+  </si>
+  <si>
+    <t>64,229,186.9</t>
+  </si>
+  <si>
+    <t>Hotels And Tourism</t>
+  </si>
+  <si>
+    <t>59,421,721.5</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>127,152,967.9</t>
-  </si>
-  <si>
-    <t>Hotels And Tourism</t>
-  </si>
-  <si>
-    <t>69,119,983.09</t>
-  </si>
-  <si>
-    <t>Manufacturing And Processing</t>
-  </si>
-  <si>
-    <t>60,815,378.7</t>
-  </si>
-  <si>
-    <t>Life Insurance</t>
-  </si>
-  <si>
-    <t>51,287,856.2</t>
+    <t>46,877,045.3</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>8,807,661.5</t>
+    <t>32,706,242.46</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>2,297,155.0</t>
+    <t>20,538,457.89</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>194,046.0</t>
+    <t>526,096.0</t>
   </si>
   <si>
     <t>Total</t>
@@ -650,208 +626,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>47,484,581.7</t>
-  </si>
-  <si>
-    <t>22,428,571.0</t>
-  </si>
-  <si>
-    <t>11,061,030.0</t>
-  </si>
-  <si>
-    <t>10,293,494.6</t>
-  </si>
-  <si>
-    <t>9,383,113.1</t>
-  </si>
-  <si>
-    <t>247,162,934.6</t>
-  </si>
-  <si>
-    <t>33,089,477.0</t>
-  </si>
-  <si>
-    <t>30,006,708.4</t>
-  </si>
-  <si>
-    <t>9,227,631.3</t>
-  </si>
-  <si>
-    <t>5,636,283.0</t>
-  </si>
-  <si>
-    <t>51,573,454.8</t>
-  </si>
-  <si>
-    <t>33,809,698.9</t>
-  </si>
-  <si>
-    <t>7,530,788.8</t>
-  </si>
-  <si>
-    <t>6,333,152.0</t>
-  </si>
-  <si>
-    <t>5,508,829.8</t>
-  </si>
-  <si>
-    <t>122,108,904.3</t>
-  </si>
-  <si>
-    <t>55,782,445.5</t>
-  </si>
-  <si>
-    <t>12,268,656.0</t>
-  </si>
-  <si>
-    <t>5,280,654.5</t>
-  </si>
-  <si>
-    <t>2,924,453.3</t>
-  </si>
-  <si>
-    <t>90,026,099.5</t>
-  </si>
-  <si>
-    <t>78,342,727.0</t>
-  </si>
-  <si>
-    <t>37,213,520.9</t>
-  </si>
-  <si>
-    <t>22,368,222.1</t>
-  </si>
-  <si>
-    <t>19,902,563.4</t>
-  </si>
-  <si>
-    <t>54,933,555.9</t>
-  </si>
-  <si>
-    <t>52,113,555.7</t>
-  </si>
-  <si>
-    <t>24,195,848.0</t>
-  </si>
-  <si>
-    <t>8,948,130.1</t>
-  </si>
-  <si>
-    <t>7,864,605.7</t>
-  </si>
-  <si>
-    <t>98,690,563.6</t>
-  </si>
-  <si>
-    <t>45,663,654.7</t>
-  </si>
-  <si>
-    <t>12,367,510.0</t>
-  </si>
-  <si>
-    <t>7,434,044.0</t>
-  </si>
-  <si>
-    <t>1,538,579.6</t>
-  </si>
-  <si>
-    <t>781,603,871.2</t>
-  </si>
-  <si>
-    <t>82,438,159.09</t>
-  </si>
-  <si>
-    <t>9,497,016.3</t>
-  </si>
-  <si>
-    <t>6,353,420.5</t>
-  </si>
-  <si>
-    <t>4,476,680.5</t>
-  </si>
-  <si>
-    <t>40,986,087.5</t>
-  </si>
-  <si>
-    <t>28,749,694.1</t>
-  </si>
-  <si>
-    <t>18,782,546.5</t>
-  </si>
-  <si>
-    <t>13,773,855.1</t>
-  </si>
-  <si>
-    <t>151,933,001.6</t>
-  </si>
-  <si>
-    <t>85,285,109.59</t>
-  </si>
-  <si>
-    <t>29,434,200.0</t>
-  </si>
-  <si>
-    <t>21,571,827.0</t>
-  </si>
-  <si>
-    <t>78,787,553.4</t>
-  </si>
-  <si>
-    <t>39,900,601.1</t>
-  </si>
-  <si>
-    <t>31,074,056.6</t>
-  </si>
-  <si>
-    <t>16,897,449.0</t>
-  </si>
-  <si>
-    <t>12,568,378.4</t>
-  </si>
-  <si>
-    <t>40,907,977.2</t>
-  </si>
-  <si>
-    <t>12,468,346.0</t>
-  </si>
-  <si>
-    <t>11,610,346.7</t>
-  </si>
-  <si>
-    <t>7,582,539.6</t>
-  </si>
-  <si>
-    <t>5,801,430.0</t>
-  </si>
-  <si>
-    <t>76,910,969.59</t>
-  </si>
-  <si>
-    <t>18,972,519.8</t>
-  </si>
-  <si>
-    <t>17,108,122.6</t>
-  </si>
-  <si>
-    <t>6,205,156.6</t>
-  </si>
-  <si>
-    <t>4,790,215.5</t>
-  </si>
-  <si>
-    <t>30,553,056.5</t>
-  </si>
-  <si>
-    <t>26,668,978.0</t>
-  </si>
-  <si>
-    <t>14,654,014.2</t>
-  </si>
-  <si>
-    <t>10,355,923.0</t>
-  </si>
-  <si>
-    <t>7,994,198.0</t>
+    <t>84,566,635.86</t>
+  </si>
+  <si>
+    <t>72,229,190.09</t>
+  </si>
+  <si>
+    <t>21,282,228.6</t>
+  </si>
+  <si>
+    <t>14,686,304.2</t>
+  </si>
+  <si>
+    <t>12,142,366.6</t>
+  </si>
+  <si>
+    <t>60,209,573.5</t>
+  </si>
+  <si>
+    <t>47,083,122.17</t>
+  </si>
+  <si>
+    <t>17,147,657.5</t>
+  </si>
+  <si>
+    <t>11,767,080.3</t>
+  </si>
+  <si>
+    <t>8,664,540.6</t>
+  </si>
+  <si>
+    <t>57,917,060.6</t>
+  </si>
+  <si>
+    <t>45,707,804.55</t>
+  </si>
+  <si>
+    <t>14,513,251.1</t>
+  </si>
+  <si>
+    <t>9,833,339.69</t>
+  </si>
+  <si>
+    <t>7,584,685.1</t>
+  </si>
+  <si>
+    <t>47,949,039.8</t>
+  </si>
+  <si>
+    <t>37,595,338.2</t>
+  </si>
+  <si>
+    <t>21,213,292.89</t>
+  </si>
+  <si>
+    <t>5,900,351.0</t>
+  </si>
+  <si>
+    <t>5,887,200.8</t>
+  </si>
+  <si>
+    <t>52,849,209.3</t>
+  </si>
+  <si>
+    <t>36,749,940.6</t>
+  </si>
+  <si>
+    <t>22,491,096.1</t>
+  </si>
+  <si>
+    <t>14,794,727.2</t>
+  </si>
+  <si>
+    <t>9,199,265.1</t>
+  </si>
+  <si>
+    <t>48,194,551.9</t>
+  </si>
+  <si>
+    <t>43,983,316.6</t>
+  </si>
+  <si>
+    <t>20,347,559.2</t>
+  </si>
+  <si>
+    <t>7,337,310.4</t>
+  </si>
+  <si>
+    <t>6,177,352.1</t>
+  </si>
+  <si>
+    <t>47,864,649.3</t>
+  </si>
+  <si>
+    <t>24,356,744.4</t>
+  </si>
+  <si>
+    <t>23,837,328.8</t>
+  </si>
+  <si>
+    <t>8,127,969.5</t>
+  </si>
+  <si>
+    <t>8,125,152.9</t>
+  </si>
+  <si>
+    <t>73,660,161.09</t>
+  </si>
+  <si>
+    <t>55,921,222.3</t>
+  </si>
+  <si>
+    <t>15,917,873.9</t>
+  </si>
+  <si>
+    <t>15,120,807.1</t>
+  </si>
+  <si>
+    <t>8,646,478.9</t>
+  </si>
+  <si>
+    <t>64,067,310.1</t>
+  </si>
+  <si>
+    <t>46,146,912.7</t>
+  </si>
+  <si>
+    <t>26,863,639.0</t>
+  </si>
+  <si>
+    <t>13,651,984.4</t>
+  </si>
+  <si>
+    <t>12,166,103.6</t>
+  </si>
+  <si>
+    <t>61,682,497.6</t>
+  </si>
+  <si>
+    <t>38,623,477.5</t>
+  </si>
+  <si>
+    <t>25,664,134.3</t>
+  </si>
+  <si>
+    <t>12,422,505.4</t>
+  </si>
+  <si>
+    <t>11,322,388.4</t>
+  </si>
+  <si>
+    <t>63,202,940.07</t>
+  </si>
+  <si>
+    <t>56,211,960.8</t>
+  </si>
+  <si>
+    <t>11,956,732.8</t>
+  </si>
+  <si>
+    <t>10,678,593.6</t>
+  </si>
+  <si>
+    <t>9,451,878.5</t>
+  </si>
+  <si>
+    <t>37,518,146.2</t>
+  </si>
+  <si>
+    <t>27,827,702.3</t>
+  </si>
+  <si>
+    <t>18,197,141.1</t>
+  </si>
+  <si>
+    <t>17,179,954.8</t>
+  </si>
+  <si>
+    <t>13,180,743.8</t>
+  </si>
+  <si>
+    <t>51,754,956.2</t>
+  </si>
+  <si>
+    <t>32,069,525.1</t>
+  </si>
+  <si>
+    <t>15,140,852.9</t>
+  </si>
+  <si>
+    <t>10,394,848.0</t>
+  </si>
+  <si>
+    <t>8,359,650.9</t>
+  </si>
+  <si>
+    <t>43,668,306.7</t>
+  </si>
+  <si>
+    <t>39,154,936.0</t>
+  </si>
+  <si>
+    <t>12,013,197.5</t>
+  </si>
+  <si>
+    <t>8,976,284.8</t>
+  </si>
+  <si>
+    <t>6,574,298.1</t>
   </si>
 </sst>
 </file>
@@ -1660,61 +1642,61 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.02430135334818088</v>
+        <v>0.03482027402365881</v>
       </c>
       <c r="E9" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>65</v>
-      </c>
       <c r="G9" s="12">
-        <v>0.4006107696064939</v>
+        <v>0.06152573822547189</v>
       </c>
       <c r="H9" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="I9" s="13" t="s">
-        <v>74</v>
-      </c>
       <c r="J9" s="14">
-        <v>0.05160031175943253</v>
+        <v>0.05560357022698711</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="L9" s="15" t="s">
         <v>81</v>
       </c>
       <c r="M9" s="16">
-        <v>0.140672201934211</v>
+        <v>0.03106117794878466</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P9" s="18">
-        <v>0.2294564507624646</v>
+        <v>0.08581405381713579</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S9" s="16">
-        <v>0.0845773998294217</v>
+        <v>0.05859038777740071</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1748643890227833</v>
+        <v>0.08502378043679276</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1726,25 +1708,25 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.01871602355571291</v>
+        <v>0.02696083376677924</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>67</v>
-      </c>
       <c r="G10" s="12">
-        <v>0.05947267369621267</v>
+        <v>0.0243233697097195</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="I10" s="13" t="s">
         <v>75</v>
       </c>
       <c r="J10" s="14">
-        <v>0.02143331946891551</v>
+        <v>0.02422982269277653</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>82</v>
@@ -1753,34 +1735,34 @@
         <v>83</v>
       </c>
       <c r="M10" s="16">
-        <v>0.1171084618530121</v>
+        <v>0.01958725197153978</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P10" s="18">
-        <v>0.216708736316425</v>
+        <v>0.02070427854522486</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="S10" s="16">
-        <v>0.07304484054732294</v>
+        <v>0.04203311364854694</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1136145791544856</v>
+        <v>0.02258448347276383</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1792,16 +1774,16 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.007083660512402733</v>
+        <v>0.02052038648647161</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>69</v>
-      </c>
       <c r="G11" s="12">
-        <v>0.05131185668242949</v>
+        <v>0.01691816660612898</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>76</v>
@@ -1810,7 +1792,7 @@
         <v>77</v>
       </c>
       <c r="J11" s="14">
-        <v>0.02133618414102735</v>
+        <v>0.01572185415149501</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>84</v>
@@ -1819,34 +1801,34 @@
         <v>85</v>
       </c>
       <c r="M11" s="16">
-        <v>0.06167198845764869</v>
+        <v>0.01905492111720547</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P11" s="18">
-        <v>0.05876429523859147</v>
+        <v>0.01907692468353992</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="R11" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="S11" s="16">
+        <v>0.01312296258857266</v>
+      </c>
+      <c r="T11" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="U11" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="S11" s="16">
-        <v>0.07164641503527595</v>
-      </c>
-      <c r="T11" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="U11" s="17" t="s">
-        <v>112</v>
-      </c>
       <c r="V11" s="18">
-        <v>0.1018331299693779</v>
+        <v>0.01748353625710144</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1858,25 +1840,25 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.007037581693817437</v>
+        <v>0.01674000486854324</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="G12" s="12">
-        <v>0.02101843998455806</v>
+        <v>0.01601579431190515</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J12" s="14">
-        <v>0.01213950516101285</v>
+        <v>0.01186010456489634</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>86</v>
@@ -1885,34 +1867,34 @@
         <v>87</v>
       </c>
       <c r="M12" s="16">
-        <v>0.02854634305011643</v>
+        <v>0.01496490997699597</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="P12" s="18">
-        <v>0.05137572443514602</v>
+        <v>0.01690675944973866</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="R12" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="S12" s="16">
+        <v>0.01184279177071946</v>
+      </c>
+      <c r="T12" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="S12" s="16">
-        <v>0.04212090972758615</v>
-      </c>
-      <c r="T12" s="17" t="s">
-        <v>113</v>
-      </c>
       <c r="U12" s="17" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="V12" s="18">
-        <v>0.03859572015476018</v>
+        <v>0.01475996470215116</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1924,7 +1906,7 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.006774645302646615</v>
+        <v>0.01654100430774616</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>71</v>
@@ -1933,52 +1915,52 @@
         <v>72</v>
       </c>
       <c r="G13" s="12">
-        <v>0.01713756471021992</v>
+        <v>0.01380229122885519</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>80</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01211802140999342</v>
+        <v>0.01140895360160138</v>
       </c>
       <c r="K13" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="L13" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="L13" s="15" t="s">
-        <v>89</v>
-      </c>
       <c r="M13" s="16">
-        <v>0.02338985231020904</v>
+        <v>0.01436654903652722</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="P13" s="18">
-        <v>0.02905234140924217</v>
+        <v>0.01565439658820465</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="S13" s="16">
-        <v>0.0286527044363502</v>
+        <v>0.01122018385835918</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01397514956555296</v>
+        <v>0.01276069463847355</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1989,7 +1971,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -1998,7 +1980,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -2007,7 +1989,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2016,7 +1998,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2025,7 +2007,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2034,7 +2016,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2043,7 +2025,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2052,566 +2034,566 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D16" s="10">
-        <v>0.7539729242659824</v>
+        <v>0.05473453093853992</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>123</v>
+        <v>54</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G16" s="12">
-        <v>0.05222210401844476</v>
+        <v>0.04193440131261324</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1889981378548237</v>
+        <v>0.04742619655620809</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="M16" s="16">
-        <v>0.0962603678042747</v>
+        <v>0.06934370774491345</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="P16" s="18">
-        <v>0.08284231011059566</v>
+        <v>0.05236895302663803</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="S16" s="16">
-        <v>0.09665242214298429</v>
+        <v>0.06786573957406927</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="V16" s="18">
-        <v>0.07926907018042084</v>
+        <v>0.05937929574142892</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D17" s="10">
-        <v>0.04692866432399449</v>
+        <v>0.03142836611752289</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="G17" s="12">
-        <v>0.03217522538421095</v>
+        <v>0.02704348553014115</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="J17" s="14">
-        <v>0.07074676446593391</v>
+        <v>0.02936703278615735</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>140</v>
+        <v>54</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="M17" s="16">
-        <v>0.06894899785300096</v>
+        <v>0.05663753292687389</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="P17" s="18">
-        <v>0.03516230570170292</v>
+        <v>0.04221808817018585</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="S17" s="16">
-        <v>0.08954381826732147</v>
+        <v>0.02732520054970272</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="V17" s="18">
-        <v>0.04441418715638891</v>
+        <v>0.04272454325412324</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0.01918100096556387</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="G18" s="12">
+        <v>0.01963386255191905</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="J18" s="14">
+        <v>0.02060269449794965</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="M18" s="16">
+        <v>0.03106086878504351</v>
+      </c>
+      <c r="N18" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="D18" s="10">
-        <v>0.02358152357132903</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="G18" s="12">
-        <v>0.02660068335282347</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="J18" s="14">
-        <v>0.06554535368819119</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="L18" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="M18" s="16">
-        <v>0.03605783947591121</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>66</v>
-      </c>
       <c r="O18" s="17" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="P18" s="18">
-        <v>0.02138933764844235</v>
+        <v>0.03802692552398265</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>155</v>
+        <v>71</v>
       </c>
       <c r="R18" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="S18" s="16">
+        <v>0.01953980395739644</v>
+      </c>
+      <c r="T18" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="U18" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="S18" s="16">
-        <v>0.03355958999533479</v>
-      </c>
-      <c r="T18" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="U18" s="17" t="s">
-        <v>164</v>
-      </c>
       <c r="V18" s="18">
-        <v>0.02228813141523413</v>
+        <v>0.03837867049811025</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D19" s="10">
-        <v>0.02043935146179428</v>
+        <v>0.01887915180934754</v>
       </c>
       <c r="E19" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.01926350351940189</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="J19" s="14">
+        <v>0.01894611401937187</v>
+      </c>
+      <c r="K19" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="F19" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="G19" s="12">
-        <v>0.01777337311414437</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="J19" s="14">
-        <v>0.06034334149071569</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>107</v>
-      </c>
       <c r="L19" s="15" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="M19" s="16">
-        <v>0.03410364568949065</v>
+        <v>0.02839234465413679</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="P19" s="18">
-        <v>0.01264864781012073</v>
+        <v>0.01664077656321915</v>
       </c>
       <c r="Q19" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="R19" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="S19" s="16">
+        <v>0.01463663311881031</v>
+      </c>
+      <c r="T19" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="R19" s="15" t="s">
+      <c r="U19" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="S19" s="16">
-        <v>0.02972964932243739</v>
-      </c>
-      <c r="T19" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="U19" s="17" t="s">
-        <v>165</v>
-      </c>
       <c r="V19" s="18">
-        <v>0.0207713575300858</v>
+        <v>0.02346333082248683</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D20" s="10">
-        <v>0.005093252652717862</v>
+        <v>0.01425562294511325</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>130</v>
+        <v>84</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="G20" s="12">
-        <v>0.01529013575591577</v>
+        <v>0.01467173401609511</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="J20" s="14">
-        <v>0.04025825157533437</v>
+        <v>0.01735688732751899</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M20" s="16">
-        <v>0.0313062859422559</v>
+        <v>0.02697686363695229</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="P20" s="18">
-        <v>0.0100484623085222</v>
+        <v>0.0154741731705989</v>
       </c>
       <c r="Q20" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="R20" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="S20" s="16">
+        <v>0.01355692025767204</v>
+      </c>
+      <c r="T20" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="U20" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="R20" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="S20" s="16">
-        <v>0.01594823819138321</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="U20" s="17" t="s">
-        <v>166</v>
-      </c>
       <c r="V20" s="18">
-        <v>0.01843539767674834</v>
+        <v>0.0201497696832694</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>60</v>
+        <v>157</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>175</v>
+        <v>71</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D31" s="22">
-        <v>0.3652383099535493</v>
+        <v>0.3126187116412152</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D32" s="22">
-        <v>0.267199386331088</v>
+        <v>0.2388105136591484</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D33" s="22">
-        <v>0.05534156358809048</v>
+        <v>0.1014886543548106</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D34" s="22">
-        <v>0.04923781416061085</v>
+        <v>0.06507357087266545</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D35" s="22">
-        <v>0.04713884285155817</v>
+        <v>0.05811711538557707</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D36" s="22">
-        <v>0.04543111386488218</v>
+        <v>0.05645230530018171</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="D37" s="22">
-        <v>0.04347628507394401</v>
+        <v>0.05098948571777414</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D38" s="22">
-        <v>0.03164239470324347</v>
+        <v>0.04931867789335771</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="D39" s="22">
-        <v>0.02626363554778714</v>
+        <v>0.02080172313954334</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D40" s="22">
-        <v>0.01427683580799537</v>
+        <v>0.01326663454367001</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D41" s="22">
-        <v>0.01256150735807919</v>
+        <v>0.01227364538062117</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D42" s="22">
-        <v>0.0105935833469768</v>
+        <v>0.009682523763696655</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D43" s="22">
-        <v>0.001819235645731838</v>
+        <v>0.006755523259060326</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D44" s="22">
-        <v>0.0004744807983107798</v>
+        <v>0.004242249173636234</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D45" s="22">
-        <v>4.008049129859047E-05</v>
+        <v>0.000108665915041914</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -2990,331 +2972,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="D9" s="10">
-        <v>0.047649745438237</v>
+        <v>0.1899163198636536</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="G9" s="12">
-        <v>0.5092255278466947</v>
+        <v>0.1577467495497759</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1153917165314197</v>
+        <v>0.1687590674349541</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="M9" s="16">
-        <v>0.2939296834232303</v>
+        <v>0.1480929523391005</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="P9" s="18">
-        <v>0.2639289889312395</v>
+        <v>0.1736860506106586</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1879837174095973</v>
+        <v>0.1660202056424933</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="V9" s="18">
-        <v>0.3528565357203816</v>
+        <v>0.1885287399231999</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D10" s="10">
-        <v>0.02250658340944013</v>
+        <v>0.1622093847180294</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="G10" s="12">
-        <v>0.06817367830158488</v>
+        <v>0.1233559556932004</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="J10" s="14">
-        <v>0.07564665207345105</v>
+        <v>0.1331836662711635</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="M10" s="16">
-        <v>0.1342745366554616</v>
+        <v>0.1161150390382784</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="P10" s="18">
-        <v>0.2296769141622771</v>
+        <v>0.1207766800588689</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="S10" s="16">
-        <v>0.1783336208155079</v>
+        <v>0.1515133760745868</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1632650419454462</v>
+        <v>0.09593606967811745</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D11" s="10">
-        <v>0.01109950314218947</v>
+        <v>0.04779476554914949</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="G11" s="12">
-        <v>0.06182230336705125</v>
+        <v>0.04492619820696515</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="J11" s="14">
-        <v>0.01684957212654271</v>
+        <v>0.04228879531716639</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="M11" s="16">
-        <v>0.02953201647972297</v>
+        <v>0.06551829165920189</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="P11" s="18">
-        <v>0.1090986613910619</v>
+        <v>0.07391576349494763</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="S11" s="16">
-        <v>0.08279867156601763</v>
+        <v>0.07009310865087237</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="V11" s="18">
-        <v>0.04421858154316161</v>
+        <v>0.09389020138081328</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D12" s="10">
-        <v>0.01032929805423277</v>
+        <v>0.03298190613470289</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="G12" s="12">
-        <v>0.01901152948811598</v>
+        <v>0.03082929443132831</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="J12" s="14">
-        <v>0.01416995008708228</v>
+        <v>0.02865244230890944</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="M12" s="16">
-        <v>0.01271112139078015</v>
+        <v>0.01822352237024284</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="P12" s="18">
-        <v>0.06557678579690557</v>
+        <v>0.04862206589777848</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="S12" s="16">
-        <v>0.03062067860898682</v>
+        <v>0.02527550798684374</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="V12" s="18">
-        <v>0.02657955245716003</v>
+        <v>0.03201435444277247</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D13" s="10">
-        <v>0.009415750010348872</v>
+        <v>0.02726883428264761</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="G13" s="12">
-        <v>0.01161233657632884</v>
+        <v>0.02270076063555018</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01232559131759848</v>
+        <v>0.02210029948004288</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="M13" s="16">
-        <v>0.007039483628017627</v>
+        <v>0.01818290733498931</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="P13" s="18">
-        <v>0.05834822861898947</v>
+        <v>0.03023288417939425</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="S13" s="16">
-        <v>0.02691283663009167</v>
+        <v>0.02127969294322016</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="V13" s="18">
-        <v>0.005501010915151472</v>
+        <v>0.03200326045051235</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3325,7 +3307,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3334,7 +3316,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3343,7 +3325,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3352,7 +3334,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3361,7 +3343,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3370,7 +3352,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3379,7 +3361,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3388,331 +3370,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="D16" s="10">
-        <v>0.7843224929623963</v>
+        <v>0.1654230013339431</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="G16" s="12">
-        <v>0.0844429286103739</v>
+        <v>0.1678538699609378</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="J16" s="14">
-        <v>0.3399386354934466</v>
+        <v>0.1797308196271756</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1896503843131516</v>
+        <v>0.1952053686688745</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="P16" s="18">
-        <v>0.1199296773000612</v>
+        <v>0.1233013459618835</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="S16" s="16">
-        <v>0.263190862818049</v>
+        <v>0.1782850578042668</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1092388702526275</v>
+        <v>0.1720002330975154</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="D17" s="10">
-        <v>0.08272490048094665</v>
+        <v>0.1255856122629173</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="G17" s="12">
-        <v>0.05923249850223904</v>
+        <v>0.1209031231583508</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="J17" s="14">
-        <v>0.1908190023235415</v>
+        <v>0.1125413129822223</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="M17" s="16">
-        <v>0.09604517473112398</v>
+        <v>0.1736133875957572</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="P17" s="18">
-        <v>0.03655337698402522</v>
+        <v>0.09145422938344966</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="S17" s="16">
-        <v>0.06492433890723592</v>
+        <v>0.1104728427189527</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="V17" s="18">
-        <v>0.09535180310068744</v>
+        <v>0.1542230195731015</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D18" s="10">
-        <v>0.009530049395334306</v>
+        <v>0.03574771540098135</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>124</v>
+        <v>245</v>
       </c>
       <c r="G18" s="12">
-        <v>0.05222210401844476</v>
+        <v>0.07038169325893985</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="J18" s="14">
-        <v>0.06585680319265939</v>
+        <v>0.07478030352585642</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="M18" s="16">
-        <v>0.07479870261282445</v>
+        <v>0.03692895349036291</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="P18" s="18">
-        <v>0.03403798545856308</v>
+        <v>0.05980391404008945</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="S18" s="16">
-        <v>0.05854433472505546</v>
+        <v>0.05215708857043531</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="V18" s="18">
-        <v>0.05239370914899993</v>
+        <v>0.04731744659672113</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="D19" s="10">
-        <v>0.006375519350675389</v>
+        <v>0.0339576951193173</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="G19" s="12">
-        <v>0.03869735634611448</v>
+        <v>0.03576767013644845</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="J19" s="14">
-        <v>0.04826533641971231</v>
+        <v>0.03619676835791771</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="M19" s="16">
-        <v>0.04067403490107462</v>
+        <v>0.03298135811790383</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="P19" s="18">
-        <v>0.02222968696049177</v>
+        <v>0.05646098661464037</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="S19" s="16">
-        <v>0.02123416890943879</v>
+        <v>0.03580808897576783</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="V19" s="18">
-        <v>0.03702638814362817</v>
+        <v>0.0353556891627695</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="D20" s="10">
-        <v>0.004492251560327413</v>
+        <v>0.01941791151755451</v>
       </c>
       <c r="E20" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0.03187472001584311</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="J20" s="14">
+        <v>0.03299124105618617</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="M20" s="16">
+        <v>0.02919258859101218</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="O20" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="P20" s="18">
+        <v>0.04331779727748784</v>
+      </c>
+      <c r="Q20" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="F20" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G20" s="12">
-        <v>0.02837803591033017</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="J20" s="14">
-        <v>0.04025825157533437</v>
-      </c>
-      <c r="K20" s="15" t="s">
+      <c r="R20" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="S20" s="16">
+        <v>0.0287972583373569</v>
+      </c>
+      <c r="T20" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="L20" s="15" t="s">
-        <v>263</v>
-      </c>
-      <c r="M20" s="16">
-        <v>0.03025348155757194</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="O20" s="17" t="s">
-        <v>268</v>
-      </c>
-      <c r="P20" s="18">
-        <v>0.01700801837199845</v>
-      </c>
-      <c r="Q20" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="R20" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="S20" s="16">
-        <v>0.01639221241243319</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>194</v>
-      </c>
       <c r="U20" s="17" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="V20" s="18">
-        <v>0.02858231738928688</v>
+        <v>0.02589477108469041</v>
       </c>
     </row>
   </sheetData>
